--- a/artfynd/A 27272-2024 artfynd.xlsx
+++ b/artfynd/A 27272-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>81745641</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>389972.9164146394</v>
+        <v>389973</v>
       </c>
       <c r="R3" t="n">
-        <v>6656137.81171258</v>
+        <v>6656138</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +869,9 @@
           <t>2019-09-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 27272-2024 artfynd.xlsx
+++ b/artfynd/A 27272-2024 artfynd.xlsx
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81745663</v>
+        <v>81745641</v>
       </c>
       <c r="B2" t="n">
-        <v>57193</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206004</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>389996.8072227698</v>
+        <v>389973</v>
       </c>
       <c r="R2" t="n">
-        <v>6656099.090762835</v>
+        <v>6656138</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +748,9 @@
           <t>2019-09-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81745641</v>
+        <v>81745658</v>
       </c>
       <c r="B3" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>389973</v>
+        <v>389966</v>
       </c>
       <c r="R3" t="n">
-        <v>6656138</v>
+        <v>6656140</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,43 +879,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81745658</v>
+        <v>81745663</v>
       </c>
       <c r="B4" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>206004</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -943,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>389965.9692196804</v>
+        <v>389997</v>
       </c>
       <c r="R4" t="n">
-        <v>6656140.019576994</v>
+        <v>6656099</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,19 +951,9 @@
           <t>2019-09-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
